--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513268_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513268_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. DUSCAK</t>
+          <t>G. PARHAM II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1043</v>
+        <v>3.3768</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5229</v>
+        <v>1.6829</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5814</v>
+        <v>1.6939</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3507</v>
+        <v>1.4615</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1608</v>
+        <v>-1.113</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1899</v>
+        <v>2.5745</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0595</v>
+        <v>1.4534</v>
       </c>
       <c r="K2" t="n">
-        <v>2.3724</v>
+        <v>-1.1668</v>
       </c>
       <c r="L2" t="n">
-        <v>1.6871</v>
+        <v>2.6201</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.7089</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.2116</v>
+        <v>0.0538</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4973</v>
+        <v>-0.0457</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.4405</v>
+        <v>1.1014</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7622</v>
+        <v>1.1014</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4497</v>
+        <v>0.8139</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9216</v>
+        <v>0.2296</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5281</v>
+        <v>0.5843</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7444</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7444</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. COSIALLS BORRAS</t>
+          <t>C. HERMANSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0662</v>
+        <v>3.1249</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6947</v>
+        <v>1.5386</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3715</v>
+        <v>1.5864</v>
       </c>
       <c r="G3" t="n">
-        <v>2.412</v>
+        <v>1.185</v>
       </c>
       <c r="H3" t="n">
-        <v>3.1922</v>
+        <v>-0.6194</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.7801</v>
+        <v>1.8044</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5647</v>
+        <v>2.3377</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4508</v>
+        <v>0.1078</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1139</v>
+        <v>2.2298</v>
       </c>
       <c r="M3" t="n">
         <v>-1.1527</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2586</v>
+        <v>-0.7272999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.894</v>
+        <v>-0.4254</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6608000000000001</v>
+        <v>1.5419</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.1014</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7622</v>
+        <v>2.6433</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1783</v>
+        <v>-0.3464</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7687</v>
+        <v>-0.4422</v>
       </c>
       <c r="U3" t="n">
-        <v>0.947</v>
+        <v>0.0958</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.185</v>
+        <v>0.7444</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.7444</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.185</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. HERMANSON</t>
+          <t>D. DUSCAK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8554</v>
+        <v>2.9428</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2402</v>
+        <v>2.6496</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6152</v>
+        <v>0.2932</v>
       </c>
       <c r="G4" t="n">
-        <v>1.185</v>
+        <v>2.3507</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6194</v>
+        <v>2.1608</v>
       </c>
       <c r="I4" t="n">
-        <v>1.8044</v>
+        <v>0.1899</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3377</v>
+        <v>4.0595</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1078</v>
+        <v>2.3724</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2298</v>
+        <v>1.6871</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1527</v>
+        <v>-1.7089</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.2116</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4254</v>
+        <v>-1.4973</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5419</v>
+        <v>-0.4405</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1014</v>
+        <v>-2.2027</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6433</v>
+        <v>1.7622</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.616</v>
+        <v>0.2882</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7406</v>
+        <v>0.0484</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1246</v>
+        <v>0.2399</v>
       </c>
       <c r="V4" t="n">
         <v>0.7444</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. PARHAM II</t>
+          <t>R. COSIALLS BORRAS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3298</v>
+        <v>2.9258</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0971</v>
+        <v>1.929</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2327</v>
+        <v>0.9968</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4615</v>
+        <v>2.412</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.113</v>
+        <v>3.1922</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5745</v>
+        <v>-0.7801</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4534</v>
+        <v>3.5647</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1668</v>
+        <v>3.4508</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6201</v>
+        <v>0.1139</v>
       </c>
       <c r="M5" t="n">
-        <v>0.008200000000000001</v>
+        <v>-1.1527</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0538</v>
+        <v>-0.2586</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0457</v>
+        <v>-0.894</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1014</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1014</v>
+        <v>1.7622</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2331</v>
+        <v>0.0379</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3562</v>
+        <v>-0.5343</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1231</v>
+        <v>0.5723</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.185</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.185</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.269</v>
+        <v>0.6388</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1516</v>
+        <v>0.8097</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1174</v>
+        <v>-0.1709</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3671</v>
@@ -922,13 +922,13 @@
         <v>1.1014</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4511</v>
+        <v>0.821</v>
       </c>
       <c r="T6" t="n">
-        <v>1.923</v>
+        <v>0.5810999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5281</v>
+        <v>0.2399</v>
       </c>
       <c r="V6" t="n">
         <v>0.185</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. LOBACO MUÑOZ</t>
+          <t>F. NWAOKORIE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,58 +955,58 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2696</v>
+        <v>0.3485</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2696</v>
+        <v>0.7573</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-0.4089</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2696</v>
+        <v>0.6378</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2696</v>
+        <v>0.2211</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.4167</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2696</v>
+        <v>3.4772</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2696</v>
+        <v>2.1208</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.3564</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>-2.8394</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-1.8997</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0.9397</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-0.2203</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-2.2027</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.9825</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-0.5172</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.4481</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ARIAS GONZALEZ</t>
+          <t>R. LOBACO MUÑOZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,28 +1033,28 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.018</v>
+        <v>0.2696</v>
       </c>
       <c r="E8" t="n">
-        <v>0.018</v>
+        <v>0.2696</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.018</v>
+        <v>0.2696</v>
       </c>
       <c r="H8" t="n">
-        <v>0.018</v>
+        <v>0.2696</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.018</v>
+        <v>0.2696</v>
       </c>
       <c r="K8" t="n">
-        <v>0.018</v>
+        <v>0.2696</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. NWAOKORIE</t>
+          <t>J. ARIAS GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3778</v>
+        <v>0.018</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4058</v>
+        <v>0.018</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7836</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6378</v>
+        <v>0.018</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2211</v>
+        <v>0.018</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4167</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>3.4772</v>
+        <v>0.018</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1208</v>
+        <v>0.018</v>
       </c>
       <c r="L9" t="n">
-        <v>1.3564</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.8394</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.8997</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9397</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2203</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2027</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.9825</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7953</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8687</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0733</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8006</v>
+        <v>-1.3293</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6357</v>
+        <v>-2.3373</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8351</v>
+        <v>1.008</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7878</v>
@@ -1234,13 +1234,13 @@
         <v>0.8811</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8939</v>
+        <v>-0.4226</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3843</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.3366</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9769</v>
+        <v>-2.5902</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3575</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6194</v>
+        <v>-1.6482</v>
       </c>
       <c r="G11" t="n">
         <v>-2.7648</v>
@@ -1312,13 +1312,13 @@
         <v>1.1014</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9565</v>
+        <v>-0.5698</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9608</v>
+        <v>-0.5453</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0043</v>
+        <v>-0.0245</v>
       </c>
       <c r="V11" t="n">
         <v>0.7444</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1855</v>
+        <v>-2.834</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4932</v>
+        <v>-2.1417</v>
       </c>
       <c r="F12" t="n">
         <v>-0.6923</v>
@@ -1390,10 +1390,10 @@
         <v>1.9825</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4046</v>
+        <v>-0.0531</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8046</v>
+        <v>-0.4531</v>
       </c>
       <c r="U12" t="n">
         <v>0.4</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.571500000000001</v>
+        <v>6.891700000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>3.913500000000001</v>
+        <v>4.2337</v>
       </c>
       <c r="F13" t="n">
-        <v>2.658000000000001</v>
+        <v>2.658</v>
       </c>
       <c r="G13" t="n">
         <v>6.546100000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9404000000000006</v>
+        <v>-0.9404000000000001</v>
       </c>
       <c r="I13" t="n">
         <v>7.486399999999999</v>
@@ -1468,13 +1468,13 @@
         <v>14.318</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1796999999999995</v>
+        <v>0.5</v>
       </c>
       <c r="T13" t="n">
-        <v>-2.0393</v>
+        <v>-1.719</v>
       </c>
       <c r="U13" t="n">
-        <v>2.2189</v>
+        <v>2.2192</v>
       </c>
       <c r="V13" t="n">
         <v>2.0482</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1701</v>
+        <v>3.5356</v>
       </c>
       <c r="E14" t="n">
-        <v>4.5715</v>
+        <v>5.0401</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4013</v>
+        <v>-1.5046</v>
       </c>
       <c r="G14" t="n">
         <v>3.587</v>
@@ -1546,13 +1546,13 @@
         <v>2.2027</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6619</v>
+        <v>-0.2964</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8968</v>
+        <v>-0.4281</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2349</v>
+        <v>0.1317</v>
       </c>
       <c r="V14" t="n">
         <v>-0.8563</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1464</v>
+        <v>3.4384</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3494</v>
+        <v>2.5837</v>
       </c>
       <c r="F15" t="n">
-        <v>0.797</v>
+        <v>0.8547</v>
       </c>
       <c r="G15" t="n">
         <v>2.9727</v>
@@ -1624,13 +1624,13 @@
         <v>1.7622</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3021</v>
+        <v>-0.0101</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6765</v>
+        <v>-0.4422</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3744</v>
+        <v>0.432</v>
       </c>
       <c r="V15" t="n">
         <v>-0.185</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.6075</v>
+        <v>2.0644</v>
       </c>
       <c r="E16" t="n">
-        <v>4.177</v>
+        <v>3.7084</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.5696</v>
+        <v>-1.644</v>
       </c>
       <c r="G16" t="n">
         <v>1.3355</v>
@@ -1702,13 +1702,13 @@
         <v>1.7622</v>
       </c>
       <c r="S16" t="n">
-        <v>0.2587</v>
+        <v>-0.2843</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2438</v>
+        <v>-0.7125</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.4281</v>
       </c>
       <c r="V16" t="n">
         <v>-0.7489</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>J. NICOLAU ALEDON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.7603</v>
+        <v>1.3416</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1524</v>
+        <v>1.4255</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9127</v>
+        <v>-0.0839</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.4589</v>
+        <v>-0.3251</v>
       </c>
       <c r="H17" t="n">
-        <v>-2.0585</v>
+        <v>-0.2751</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4004</v>
+        <v>-0.05</v>
       </c>
       <c r="J17" t="n">
-        <v>-2.1395</v>
+        <v>1.3381</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.4723</v>
+        <v>1.1862</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6672</v>
+        <v>0.1519</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3194</v>
+        <v>-1.6632</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.5862000000000001</v>
+        <v>-1.4613</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2668</v>
+        <v>-0.2019</v>
       </c>
       <c r="P17" t="n">
-        <v>1.5419</v>
+        <v>1.1014</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5419</v>
+        <v>1.1014</v>
       </c>
       <c r="S17" t="n">
-        <v>2.7892</v>
+        <v>0.4878</v>
       </c>
       <c r="T17" t="n">
-        <v>1.987</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.8021</v>
+        <v>0.4003</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1119</v>
+        <v>0.0776</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1119</v>
+        <v>0.0776</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. NICOLAU ALEDON</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.257</v>
+        <v>0.2427</v>
       </c>
       <c r="E18" t="n">
-        <v>1.5427</v>
+        <v>-1.3241</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2857</v>
+        <v>1.5668</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3251</v>
+        <v>-2.4589</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2751</v>
+        <v>-2.0585</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.05</v>
+        <v>-0.4004</v>
       </c>
       <c r="J18" t="n">
-        <v>1.3381</v>
+        <v>-2.1395</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1862</v>
+        <v>-1.4723</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1519</v>
+        <v>-0.6672</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6632</v>
+        <v>-0.3194</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.4613</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2019</v>
+        <v>0.2668</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1014</v>
+        <v>1.5419</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1014</v>
+        <v>1.5419</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4032</v>
+        <v>1.2716</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2046</v>
+        <v>0.8154</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1986</v>
+        <v>0.4562</v>
       </c>
       <c r="V18" t="n">
-        <v>0.0776</v>
+        <v>-0.1119</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0776</v>
+        <v>-0.1119</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5407</v>
+        <v>-1.9378</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4164</v>
+        <v>-1.7679</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1243</v>
+        <v>-0.1698</v>
       </c>
       <c r="G19" t="n">
         <v>-1.5878</v>
@@ -1936,13 +1936,13 @@
         <v>1.9825</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2498</v>
+        <v>-0.1472</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0405</v>
+        <v>-0.311</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2093</v>
+        <v>0.1637</v>
       </c>
       <c r="V19" t="n">
         <v>1.1189</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7978</v>
+        <v>-2.45</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.821</v>
+        <v>-2.7038</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0232</v>
+        <v>0.2538</v>
       </c>
       <c r="G20" t="n">
         <v>-1.4018</v>
@@ -2014,13 +2014,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9555</v>
+        <v>-0.6077</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.5234</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3149</v>
+        <v>-0.0843</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7935</v>
+        <v>-3.6461</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6671</v>
+        <v>-2.9642</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1264</v>
+        <v>-0.6819</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1319</v>
@@ -2092,13 +2092,13 @@
         <v>2.6433</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8889</v>
+        <v>0.2585</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9968</v>
+        <v>-0.2938</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1078</v>
+        <v>0.5523</v>
       </c>
       <c r="V21" t="n">
         <v>-0.1119</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-9.380599999999999</v>
+        <v>-8.379200000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.2415</v>
+        <v>-6.6557</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.1391</v>
+        <v>-1.7235</v>
       </c>
       <c r="G22" t="n">
         <v>-5.5357</v>
@@ -2170,13 +2170,13 @@
         <v>2.8635</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0722</v>
+        <v>-0.0708</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9968</v>
+        <v>-0.411</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.07539999999999999</v>
+        <v>0.3402</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2308</v>
@@ -2203,16 +2203,16 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.571299999999999</v>
+        <v>-5.790400000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.657800000000002</v>
+        <v>-2.658</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.9135</v>
+        <v>-3.1324</v>
       </c>
       <c r="G23" t="n">
-        <v>-6.546</v>
+        <v>-6.545999999999999</v>
       </c>
       <c r="H23" t="n">
         <v>0.9404000000000006</v>
@@ -2248,13 +2248,13 @@
         <v>16.5205</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1796999999999997</v>
+        <v>0.6014000000000002</v>
       </c>
       <c r="T23" t="n">
         <v>-2.2192</v>
       </c>
       <c r="U23" t="n">
-        <v>2.0393</v>
+        <v>2.8202</v>
       </c>
       <c r="V23" t="n">
         <v>-2.0483</v>
